--- a/reports/hazop_system_63.xlsx
+++ b/reports/hazop_system_63.xlsx
@@ -464,7 +464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAZOP preparation — System 63</t>
+          <t>HAZOP preparation — System 63 (functional loops)</t>
         </is>
       </c>
     </row>
@@ -550,16 +550,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -599,15 +602,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -636,7 +654,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -665,7 +686,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -694,7 +718,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -723,7 +750,10 @@
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
